--- a/InputData/indst/CPCC/Cement Pathway Capital Cost per Unit Annual Capacity.xlsx
+++ b/InputData/indst/CPCC/Cement Pathway Capital Cost per Unit Annual Capacity.xlsx
@@ -765,11 +765,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Construction-cost inflation index, 2009$ -&gt; 2026$ (EI judgment)</t>
+          <t>Construction-cost index, 2009$ -&gt; 2012$ (ENR CCI 8570 -&gt; 9308; the earlier 1.6 took the value to 2026$, but the model runs in 2012 USD - fixed 2026-10-01)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.6</v>
+        <v>1.086</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Deflator applied to the 2026$ judgment parameters (electric, alt chem) to reach 2012$: 1.086 / 1.6</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.6787</v>
       </c>
     </row>
     <row r="12">
@@ -852,11 +862,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNVERIFIED - EI judgment; no public cost data at any scale</t>
+          <t>UNVERIFIED - EI judgment; 450 (2026$) deflated to 2012$ and rounded</t>
         </is>
       </c>
     </row>
@@ -867,11 +877,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNVERIFIED - EI judgment (Nth-plant assumption); FOAK actuals run 5-8x higher</t>
+          <t>UNVERIFIED - EI judgment (Nth-plant); 600 (2026$) deflated to 2012$ and rounded</t>
         </is>
       </c>
     </row>
@@ -896,14 +906,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dry kiln with CCS: $/(t/yr) = total capex / capacity</t>
+          <t>Dry kiln with CCS: KILN ONLY (= dry kiln). Capture equipment priced in-model from the CCS sector (CC Capital Cost ... per t CO2/yr x captured t CO2 per t clinker). NZA $933/(t/yr) kept below as a plant-level cross-check.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unrounded ($/(t/yr))</t>
+          <t>NZA plant-level cross-check ($/(t/yr), NZA dollars, not used)</t>
         </is>
       </c>
       <c r="B2">
@@ -914,18 +924,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rounded to nearest dollar</t>
+          <t>Kiln-only value used (= dry kiln)</t>
         </is>
       </c>
       <c r="B3">
-        <f>ROUND(B2,0)</f>
+        <f>B7</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Dry kiln with precalciner: inflate 2009$ base by index, round to nearest $25</t>
+          <t>Dry kiln with precalciner: 2009$ base x 2009-&gt;2012 construction index, round to nearest $25</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1155,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unit: $/(metric ton/yr) greenfield (CCS=NZA confirmed; dry kiln 375 = ECRA-inflated SNIPPET tier; electric/alt-chem judgment, FOAK actuals 5-8x higher - see generator comments)</t>
+          <t>Unit: $/(metric ton/yr) greenfield in the model's 2012 USD (dry kiln 250 = ECRA/IEA 2009$ base 235 x 1.086 construction-cost index 2009-&gt;2012, rounded to $25; CCS row = KILN ONLY - capture equipment is priced in-model from the CCS sector's capital cost per t CO2/yr (reconciliation 2026-10-01); electric 300 / alt chem 400 = the earlier 2026$ judgments deflated; verify before release)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1161,7 +1171,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3">
@@ -1171,7 +1181,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>933</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4">
@@ -1181,7 +1191,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
@@ -1191,7 +1201,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
